--- a/data/micaja_data.xlsx
+++ b/data/micaja_data.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,6 +749,486 @@
         <v>250000</v>
       </c>
       <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hamburguesa Sencilla</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G11" t="n">
+        <v>750000</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Egreso</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nómina Empleado</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hamburguesa Sencilla</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>750000</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Egreso</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Carne x10</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Salchipapa</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>gaseoas</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hamburguesa Especial</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Salchipapa</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>tacos</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Egreso</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Arriendo Locales</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hamburguesa Especial</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Hamburguesa Especial</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Egreso</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nómina Empleado</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Gaseosa 400ml</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Gaseosa 400ml</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>400000</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>pollo frito</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -761,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,11 +1268,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hamburguesa Sencilla</t>
+          <t>Hamburguesa Especial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -801,16 +1281,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hamburguesa Especial</t>
+          <t>Salchipapa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -819,16 +1299,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Perro Caliente</t>
+          <t>Gaseosa 400ml</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,16 +1317,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Salchipapa</t>
+          <t>Jugo Natural</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -855,52 +1335,52 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gaseosa 400ml</t>
+          <t>Arriendo Locales</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Egreso</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jugo Natural</t>
+          <t>Servicios Públicos</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ingreso</t>
+          <t>Egreso</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arriendo Locales</t>
+          <t>Nómina Empleado</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -909,16 +1389,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1200000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Servicios Públicos</t>
+          <t>Pan de Hamburguesa x12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -927,16 +1407,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>300000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nómina Empleado</t>
+          <t>Carne x10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -945,16 +1425,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pan de Hamburguesa x12</t>
+          <t>Queso Tajado x50</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -963,16 +1443,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carne x10</t>
+          <t>Papas Fritas 2kg</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -981,16 +1461,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Queso Tajado x50</t>
+          <t>Salsas y Aderezos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -999,43 +1479,61 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Papas Fritas 2kg</t>
+          <t>gaseoas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egreso</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Salsas y Aderezos</t>
+          <t>tacos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egreso</t>
+          <t>Ingreso</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10000</v>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pollo frito</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ingreso</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>
